--- a/sources/forest_step6b.xlsx
+++ b/sources/forest_step6b.xlsx
@@ -3273,12 +3273,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>– ~4 [~D]</t>
+          <t>– ~4</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>– Spring Kick [PLD]</t>
+          <t>– Spring Kick</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>(~D)PLD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4729,12 +4734,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>d+3+4 [~D]</t>
+          <t>d+3+4</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Frog Man [KND]</t>
+          <t>Frog Man</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>(~D)KND</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">

--- a/sources/forest_step6b.xlsx
+++ b/sources/forest_step6b.xlsx
@@ -822,6 +822,11 @@
           <t>The initial grab does no damage.</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>c496aa41-bc15-473a-b020-7fdb437577cf</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>c496aa41-bc15-473a-b020-7fdb437577cf</t>
@@ -874,6 +879,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>daf033ef-4b67-4b29-86af-e6b2fab70477</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>daf033ef-4b67-4b29-86af-e6b2fab70477</t>
@@ -921,6 +931,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1726e35f-9e18-4c65-a787-332f9f98cc84</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>1726e35f-9e18-4c65-a787-332f9f98cc84</t>
@@ -966,6 +981,11 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>a1c6311d-6e89-4a3a-b759-44f0ce100eea</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -6709,6 +6729,11 @@
           <t>mhmhhLhhhm</t>
         </is>
       </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>3176b347-df34-4e1d-aba7-0986acc47022</t>
+        </is>
+      </c>
       <c r="R116" t="inlineStr">
         <is>
           <t>3176b347-df34-4e1d-aba7-0986acc47022</t>
@@ -6741,6 +6766,11 @@
           <t>mhmhhLmlLm</t>
         </is>
       </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>f1b78286-7ba8-4bda-bee5-c8b848d48f48</t>
+        </is>
+      </c>
       <c r="R117" t="inlineStr">
         <is>
           <t>f1b78286-7ba8-4bda-bee5-c8b848d48f48</t>
@@ -6773,6 +6803,11 @@
           <t>mhmhhLmlLm</t>
         </is>
       </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>58c32a2c-b1e2-4611-949c-911167465bf7</t>
+        </is>
+      </c>
       <c r="R118" t="inlineStr">
         <is>
           <t>58c32a2c-b1e2-4611-949c-911167465bf7</t>
@@ -6805,6 +6840,11 @@
           <t>mlmhhLhhhm</t>
         </is>
       </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>30f18387-0cd0-40f9-bf5b-9602c4d57833</t>
+        </is>
+      </c>
       <c r="R119" t="inlineStr">
         <is>
           <t>30f18387-0cd0-40f9-bf5b-9602c4d57833</t>
@@ -6837,6 +6877,11 @@
           <t>mlmhhLmhlm</t>
         </is>
       </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>a1dab966-d331-415b-9775-354f1c4d19a5</t>
+        </is>
+      </c>
       <c r="R120" t="inlineStr">
         <is>
           <t>a1dab966-d331-415b-9775-354f1c4d19a5</t>
@@ -6867,6 +6912,11 @@
       <c r="K121" t="inlineStr">
         <is>
           <t>mlmhhLmlLm</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>99593a10-9a71-4270-8908-8fdf661c902a</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
